--- a/assets/xlsx/LGI 4.xlsx
+++ b/assets/xlsx/LGI 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB BOTIKA\automate-botika\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4560D418-0934-4E42-804A-F8035D185BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D54B9B-8B03-4549-BA00-F50482D83324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>No</t>
   </si>
@@ -32,54 +32,6 @@
   </si>
   <si>
     <t>Context</t>
-  </si>
-  <si>
-    <t>cara claim gym</t>
-  </si>
-  <si>
-    <t>tanya cara klaim gym</t>
-  </si>
-  <si>
-    <t>prosedur claim gym</t>
-  </si>
-  <si>
-    <t>mau klaim gym gimana caranya</t>
-  </si>
-  <si>
-    <t>data kosong pada saat mau submit klaim disebabkan oleh apa?</t>
-  </si>
-  <si>
-    <t>kalau datanya kosong pas submit gimana</t>
-  </si>
-  <si>
-    <t>kak ini gimana ya datanya kosong pas mau submit</t>
-  </si>
-  <si>
-    <t>boleh dibantu ga kenapa data kosong pas submit</t>
-  </si>
-  <si>
-    <t>proses reimbusenya gimana ya?</t>
-  </si>
-  <si>
-    <t>cara reimburse</t>
-  </si>
-  <si>
-    <t>tolong info cara reimburs</t>
-  </si>
-  <si>
-    <t>langkah reimburse gmn</t>
-  </si>
-  <si>
-    <t>saya mendapat email untuk menambahkan nama rumah sakit dan contact, namun di menu claim status tidak ada tombol edit</t>
-  </si>
-  <si>
-    <t>mau lengkapik kekurangan klaim dmn</t>
-  </si>
-  <si>
-    <t>kak saya ada kekurangan klaim , lengkapinnya gimana</t>
-  </si>
-  <si>
-    <t>kak cara reklaim gimana sih soalnya mau nambahin kekurangan klaim</t>
   </si>
   <si>
     <t>kenapa dokumen pendukung tidak bisa diambil daei gallery?</t>
@@ -118,14 +70,17 @@
     <t>kak penjelasannya dong kalo saya hak kamar 750.000 tapi nempatin kamar di 1.200. 000 proses nya gimana ya</t>
   </si>
   <si>
-    <t>REKLAIM/ECLAIM</t>
-  </si>
-  <si>
     <t>Bapak/Ibu [username], mohon maaf atas ketidaknyamanannya. Silahkan tunggu beberapa saat dan login kembali untuk mencoba layanan yang diinginkan. Pastikan jaringan internet di sekitar Bapak/Ibu baik. Jika setelah dicoba masih ada kendala, Anda dapat mengetik Contact Center untuk terhubung dengan tim contact center kami
 [button] Contact Center</t>
   </si>
   <si>
     <t>Bapak/Ibu, detail toleransi kamar dapat dilihat dalam menu "Membership and Handbook" pada aplikasi eBenefit Anda</t>
+  </si>
+  <si>
+    <t>TECHNICAL ISSUE</t>
+  </si>
+  <si>
+    <t>TOLERANSI PLAFON</t>
   </si>
 </sst>
 </file>
@@ -301,7 +256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -339,6 +294,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -348,8 +306,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -680,317 +641,251 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="12">
+    <row r="2" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>32</v>
+      <c r="D2" s="17" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="12">
+    <row r="3" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="14"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="12">
+      <c r="D3" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2"/>
-      <c r="B5" s="12">
+      <c r="D4" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2"/>
-      <c r="B6" s="12">
+      <c r="D5" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>32</v>
+      <c r="D6" s="18" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="12">
+    <row r="7" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="8" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="12">
+      <c r="D7" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2"/>
-      <c r="B9" s="12">
+      <c r="D8" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="15"/>
-    </row>
-    <row r="10" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="12">
+      <c r="D9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>32</v>
+      <c r="D10" s="18" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="12">
+    <row r="11" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="14"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="12">
+      <c r="D11" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="14"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="12">
+      <c r="D12" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="16"/>
+      <c r="C13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="15"/>
-    </row>
-    <row r="14" spans="1:4" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="12">
-        <v>13</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="12">
-        <v>14</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="D13" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="14"/>
-    </row>
-    <row r="16" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2"/>
-      <c r="B16" s="12">
-        <v>15</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="14"/>
-    </row>
-    <row r="17" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="12"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2"/>
-      <c r="B17" s="12">
-        <v>16</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="15"/>
-    </row>
-    <row r="18" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="12"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2"/>
-      <c r="B18" s="12">
-        <v>17</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="12"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
-      <c r="B19" s="12">
-        <v>18</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="12"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2"/>
-      <c r="B20" s="12">
-        <v>19</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="12"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="13"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2"/>
-      <c r="B21" s="12">
-        <v>20</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="12"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
-      <c r="B22" s="12">
-        <v>21</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="12"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2"/>
-      <c r="B23" s="12">
-        <v>22</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
-      <c r="B24" s="12">
-        <v>23</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="12"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2"/>
-      <c r="B25" s="12">
-        <v>24</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="12"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2"/>
-      <c r="B26" s="12">
-        <v>25</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="12"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
-      <c r="B27" s="12">
-        <v>26</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="12"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2"/>
-      <c r="B28" s="12">
-        <v>27</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="12"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2"/>
-      <c r="B29" s="12">
-        <v>28</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>34</v>
-      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="13"/>
     </row>
     <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2"/>
@@ -6412,10 +6307,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D13"/>
     <mergeCell ref="D14:D17"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
